--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t>Unités de soins palliatifs</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de médecine interne</t>
   </si>
   <si>
     <t/>
@@ -1419,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B176"/>
+  <dimension ref="A1:B177"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2823,15 +2829,23 @@
         <v>376</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>378</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
